--- a/gnu_ipgyeol/gnu_입결_2020_2026.xlsx
+++ b/gnu_ipgyeol/gnu_입결_2020_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,10 +426,12 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="46" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="46" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -485,20 +487,30 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>상위누적_평균</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>학생부등급_80컷</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>상위누적_80컷</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>환산점수_평균</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>환산점수_80컷</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -555,20 +567,30 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>33.5%</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>4.29</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>960.76</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>950.65</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>2021학년도에 농학과·원예학과로 분리되기 전 통합 모집단위</t>
         </is>
@@ -625,20 +647,30 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>47.8%</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>4.65</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>53.0%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>949.08</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>945.29</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -691,20 +723,30 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>33.4%</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>3.96</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>39.3%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>961.32</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>956.27</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -757,20 +799,30 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t>35.6%</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>4.04</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>40.8%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>958.97</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>954.55</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -823,20 +875,30 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>4.36</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>47.2%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>958.23</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>949.68</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -889,20 +951,30 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>4.71</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>54.2%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>950.01</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>944.61</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -955,20 +1027,30 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t>41.4%</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>4.24</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>44.8%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>954.09</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>951.55</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1019,18 +1101,24 @@
           <t>4.01</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>40.2%</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>984.23</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>979.20</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>2021학년도에 농학과·원예학과로 분리되기 전 통합 모집단위</t>
         </is>
@@ -1085,18 +1173,24 @@
           <t>3.57</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>32.7%</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>967.84</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>965.60</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1147,18 +1241,24 @@
           <t>4.79</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>55.8%</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
         <is>
           <t>970.82</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>969.95</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1209,10 +1309,16 @@
           <t>4.49</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>49.8%</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1263,10 +1369,16 @@
           <t>4.77</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>55.4%</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1317,10 +1429,16 @@
           <t>4.61</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>52.2%</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1371,10 +1489,16 @@
           <t>4.75</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>55.0%</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1427,20 +1551,30 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t>58.4%</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>5.21</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>941.07</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>936.84</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>2022학년도부터 원예과학부로 개편</t>
         </is>
@@ -1497,20 +1631,30 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>42.8%</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>4.57</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>51.4%</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>953.6</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>946.45</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1563,20 +1707,30 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>42.4%</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>4.65</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>53.0%</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>953.23</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>945.27</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1629,20 +1783,30 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>4.73</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>54.6%</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>955.07</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>944.15</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1695,20 +1859,30 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t>61.5%</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>5.65</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>71.1%</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>938.73</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>930.1</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1761,20 +1935,30 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t>49.2%</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>4.89</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>57.8%</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>945.94</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>941.66</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1825,18 +2009,24 @@
           <t>3.77</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>36.1%</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
         <is>
           <t>960.90</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>961.10</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>2022학년도부터 원예과학부로 개편</t>
         </is>
@@ -1891,18 +2081,24 @@
           <t>4.77</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>55.4%</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
         <is>
           <t>969.84</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>967.95</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1953,10 +2149,16 @@
           <t>4.1</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>42.0%</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2007,10 +2209,16 @@
           <t>4.96</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>59.2%</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2040,7 +2248,9 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
         <is>
           <t>해당 학년도 미선발(모집요강·결과자료에 모집단위 없음)</t>
         </is>
@@ -2074,7 +2284,9 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
         <is>
           <t>해당 학년도 미선발(모집요강·결과자료에 모집단위 없음)</t>
         </is>
@@ -2131,20 +2343,30 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t>39.5%</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t>3.95</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>39.2%</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>955.46</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>955.74</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2197,20 +2419,30 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t>39.5%</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t>4.24</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>44.8%</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>955.42</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>951.45</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2263,20 +2495,30 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t>25.7%</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t>3.39</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>29.6%</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>968.03</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>964.63</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2329,20 +2571,30 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t>46.0%</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t>5.93</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>75.8%</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>950.49</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>926.1</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2395,20 +2647,30 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t>42.6%</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>48.0%</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>953.1</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>949.12</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2461,20 +2723,30 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t>37.3%</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t>4.12</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>42.4%</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>957.51</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>953.36</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2527,20 +2799,30 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t>48.0%</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t>4.92</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>58.4%</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>949.22</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>941.21</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2591,18 +2873,24 @@
           <t>4.14</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>42.8%</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
         <is>
           <t>986.72</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>988.05</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2653,18 +2941,24 @@
           <t>4.32</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>46.4%</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
         <is>
           <t>985.34</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>985.25</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2715,18 +3009,24 @@
           <t>4.37</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>47.4%</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
         <is>
           <t>992.99</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>991.4</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2777,10 +3077,16 @@
           <t>4.38</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2831,10 +3137,16 @@
           <t>4.18</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>43.6%</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2885,10 +3197,16 @@
           <t>4.72</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>54.4%</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2939,10 +3257,16 @@
           <t>4.02</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>40.4%</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
